--- a/data/trans_orig/P45C_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54314</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37698</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63353</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98547</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138761</t>
+          <t>136891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388165</t>
+          <t>389289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419462</t>
+          <t>420815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242314</t>
+          <t>242817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>269082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640683</t>
+          <t>642553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>680897</t>
+          <t>682381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>44097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73608</t>
+          <t>73428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75943</t>
+          <t>76491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98836</t>
+          <t>100266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139899</t>
+          <t>140961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293326</t>
+          <t>293506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320649</t>
+          <t>322837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295922</t>
+          <t>295374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324245</t>
+          <t>323831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>598900</t>
+          <t>597838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>639963</t>
+          <t>638533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86091</t>
+          <t>86720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124709</t>
+          <t>122155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106363</t>
+          <t>109601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146776</t>
+          <t>150236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415812</t>
+          <t>418366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454430</t>
+          <t>453801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>133845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152023</t>
+          <t>152254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561527</t>
+          <t>558067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>601940</t>
+          <t>598702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148392</t>
+          <t>151243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196986</t>
+          <t>199701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>75019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110478</t>
+          <t>113209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237659</t>
+          <t>235716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295832</t>
+          <t>295901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1038251</t>
+          <t>1035536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1083994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600663</t>
+          <t>597932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635544</t>
+          <t>636122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650546</t>
+          <t>1650477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1708719</t>
+          <t>1710662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>61372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75155</t>
+          <t>74546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110694</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290661</t>
+          <t>289662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316094</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>506640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532811</t>
+          <t>532774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>806855</t>
+          <t>806347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>842394</t>
+          <t>843003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78811</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123994</t>
+          <t>124163</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169945</t>
+          <t>166369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186107</t>
+          <t>185657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238471</t>
+          <t>236303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>215425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245145</t>
+          <t>244428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1075514</t>
+          <t>1079090</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1121465</t>
+          <t>1121296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1303493</t>
+          <t>1305661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1355857</t>
+          <t>1356307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>472070</t>
+          <t>471991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>553581</t>
+          <t>560085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>382981</t>
+          <t>381206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>458309</t>
+          <t>458407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>881263</t>
+          <t>873602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>993088</t>
+          <t>987858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2708930</t>
+          <t>2702426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2790441</t>
+          <t>2790520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2911617</t>
+          <t>2911519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2986945</t>
+          <t>2988720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5639349</t>
+          <t>5644579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5751174</t>
+          <t>5758835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72535</t>
+          <t>72932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107216</t>
+          <t>106900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56238</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111155</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152589</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328984</t>
+          <t>329300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363665</t>
+          <t>363268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256252</t>
+          <t>258299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282380</t>
+          <t>281758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596101</t>
+          <t>596149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>637535</t>
+          <t>638259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43649</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75100</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42824</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72063</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96264</t>
+          <t>96006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137931</t>
+          <t>137699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336419</t>
+          <t>336756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367870</t>
+          <t>367055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262933</t>
+          <t>262723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292172</t>
+          <t>293245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608584</t>
+          <t>608816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650251</t>
+          <t>650509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77548</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>117183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109786</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151517</t>
+          <t>152892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514485</t>
+          <t>511297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550932</t>
+          <t>548901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208003</t>
+          <t>210178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231085</t>
+          <t>230721</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>732790</t>
+          <t>731415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>774521</t>
+          <t>774528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159367</t>
+          <t>159075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211439</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92267</t>
+          <t>91717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130981</t>
+          <t>132920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266015</t>
+          <t>263135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329738</t>
+          <t>326634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>934895</t>
+          <t>936369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986967</t>
+          <t>987259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630374</t>
+          <t>628435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>669088</t>
+          <t>669638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1577951</t>
+          <t>1581055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1641674</t>
+          <t>1644554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>66348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97938</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137677</t>
+          <t>140191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185411</t>
+          <t>188112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409828</t>
+          <t>408988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442120</t>
+          <t>441418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661818</t>
+          <t>662506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>696949</t>
+          <t>696795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1080569</t>
+          <t>1077868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1128303</t>
+          <t>1125789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>72203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102291</t>
+          <t>101192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131397</t>
+          <t>130273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176189</t>
+          <t>175523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>210942</t>
+          <t>211180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>267852</t>
+          <t>269028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161588</t>
+          <t>162687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192241</t>
+          <t>191676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>916172</t>
+          <t>916838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>960964</t>
+          <t>962088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1088388</t>
+          <t>1087212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1145298</t>
+          <t>1145060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>552669</t>
+          <t>554090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642735</t>
+          <t>640850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>433176</t>
+          <t>432600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>514325</t>
+          <t>517127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1006792</t>
+          <t>1012333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1130522</t>
+          <t>1132855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2751444</t>
+          <t>2753329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2841510</t>
+          <t>2840089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3000918</t>
+          <t>2998116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3082067</t>
+          <t>3082643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5778900</t>
+          <t>5776567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5902630</t>
+          <t>5897089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57301</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87309</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54132</t>
+          <t>53379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84745</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116850</t>
+          <t>117410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159206</t>
+          <t>158700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>338014</t>
+          <t>336996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368022</t>
+          <t>369917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256896</t>
+          <t>258814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287509</t>
+          <t>288262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>607758</t>
+          <t>608264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>650114</t>
+          <t>649554</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59336</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46911</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79105</t>
+          <t>75841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>87905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125018</t>
+          <t>126554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>316073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341279</t>
+          <t>341808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289820</t>
+          <t>293084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322014</t>
+          <t>322190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>618200</t>
+          <t>616664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657163</t>
+          <t>655313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67042</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>104885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434032</t>
+          <t>435311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465762</t>
+          <t>465967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138069</t>
+          <t>137723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154986</t>
+          <t>154314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580758</t>
+          <t>577582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615425</t>
+          <t>614291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120683</t>
+          <t>120901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167260</t>
+          <t>166001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93124</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224867</t>
+          <t>226497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285114</t>
+          <t>284740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>971114</t>
+          <t>972373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1017691</t>
+          <t>1017473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690143</t>
+          <t>687524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728005</t>
+          <t>727048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1674390</t>
+          <t>1674764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1734637</t>
+          <t>1733007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45414</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78603</t>
+          <t>76084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>86701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107089</t>
+          <t>107183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152093</t>
+          <t>152496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541211</t>
+          <t>543730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>574400</t>
+          <t>574999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645984</t>
+          <t>646198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676610</t>
+          <t>676795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200619</t>
+          <t>1200216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245623</t>
+          <t>1245529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79972</t>
+          <t>80377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128044</t>
+          <t>126983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173340</t>
+          <t>173099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191812</t>
+          <t>189777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245686</t>
+          <t>243552</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202523</t>
+          <t>202118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231280</t>
+          <t>230327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>901206</t>
+          <t>901447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>946502</t>
+          <t>947563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1111355</t>
+          <t>1113489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1165229</t>
+          <t>1167264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>408912</t>
+          <t>410988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>488168</t>
+          <t>488731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>435450</t>
+          <t>437204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>517757</t>
+          <t>516017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>871402</t>
+          <t>873389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>983072</t>
+          <t>987299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2868476</t>
+          <t>2867913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2947732</t>
+          <t>2945656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2987505</t>
+          <t>2989245</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3069812</t>
+          <t>3068058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5878834</t>
+          <t>5874607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5990504</t>
+          <t>5988517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59549</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93918</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>40599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64963</t>
+          <t>64417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107894</t>
+          <t>108156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150340</t>
+          <t>149117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411294</t>
+          <t>412134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>445663</t>
+          <t>446701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>382504</t>
+          <t>383050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>407406</t>
+          <t>406868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802339</t>
+          <t>803562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844785</t>
+          <t>844523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57719</t>
+          <t>56722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>92175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>69489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110049</t>
+          <t>108415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153083</t>
+          <t>152462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360139</t>
+          <t>360038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394494</t>
+          <t>395491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311464</t>
+          <t>313091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336997</t>
+          <t>335817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>681710</t>
+          <t>682331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724744</t>
+          <t>726378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121462</t>
+          <t>122444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>36852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147021</t>
+          <t>146591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545390</t>
+          <t>544408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642037</t>
+          <t>640707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132588</t>
+          <t>133299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148353</t>
+          <t>148527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686193</t>
+          <t>686623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>790756</t>
+          <t>796362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126014</t>
+          <t>124907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174630</t>
+          <t>173361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136293</t>
+          <t>138882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174195</t>
+          <t>173292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295562</t>
+          <t>296955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855778</t>
+          <t>857047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>904394</t>
+          <t>905501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>841111</t>
+          <t>838522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>921005</t>
+          <t>924255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1712249</t>
+          <t>1710856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1833616</t>
+          <t>1834519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74752</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113784</t>
+          <t>113211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76022</t>
+          <t>75964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124288</t>
+          <t>121508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159175</t>
+          <t>156264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224068</t>
+          <t>223764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359798</t>
+          <t>360371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398830</t>
+          <t>399723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716387</t>
+          <t>719167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>764653</t>
+          <t>764711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1090189</t>
+          <t>1090493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1155082</t>
+          <t>1157993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77587</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118381</t>
+          <t>118671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123246</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183622</t>
+          <t>182911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162920</t>
+          <t>161475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>207693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>642397</t>
+          <t>642107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>678691</t>
+          <t>679597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>817663</t>
+          <t>818374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>878039</t>
+          <t>877710</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>386605</t>
+          <t>414936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578485</t>
+          <t>582146</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>356568</t>
+          <t>348669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>483595</t>
+          <t>490315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>821834</t>
+          <t>830190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1036392</t>
+          <t>1041961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2790288</t>
+          <t>2786627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2982168</t>
+          <t>2953837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3091670</t>
+          <t>3084950</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3218697</t>
+          <t>3226596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5907647</t>
+          <t>5902078</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6122205</t>
+          <t>6113849</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52961</t>
+          <t>52686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84487</t>
+          <t>84546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>37594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>97319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136891</t>
+          <t>138071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389289</t>
+          <t>389230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420815</t>
+          <t>421090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242817</t>
+          <t>242582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269082</t>
+          <t>268073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>642553</t>
+          <t>641373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682381</t>
+          <t>682125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44097</t>
+          <t>45664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73428</t>
+          <t>73994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76491</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100266</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140961</t>
+          <t>139330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293506</t>
+          <t>292940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322837</t>
+          <t>321270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295374</t>
+          <t>298245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323831</t>
+          <t>323753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597838</t>
+          <t>599469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638533</t>
+          <t>639517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86720</t>
+          <t>85663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122155</t>
+          <t>123866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109601</t>
+          <t>108410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150236</t>
+          <t>148304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418366</t>
+          <t>416655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453801</t>
+          <t>454858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>134305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152254</t>
+          <t>152274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558067</t>
+          <t>559999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>598702</t>
+          <t>599893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>150115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199701</t>
+          <t>199631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75019</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>111105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235716</t>
+          <t>236068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295901</t>
+          <t>295811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1035536</t>
+          <t>1035606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1083994</t>
+          <t>1085122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597932</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>636122</t>
+          <t>635693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650477</t>
+          <t>1650567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1710662</t>
+          <t>1710310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59875</t>
+          <t>60789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>34773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61372</t>
+          <t>61059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>76547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>111868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289662</t>
+          <t>288748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315456</t>
+          <t>315735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>506640</t>
+          <t>506953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532774</t>
+          <t>533239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>806347</t>
+          <t>805681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>843003</t>
+          <t>841002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81080</t>
+          <t>79972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124163</t>
+          <t>126948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166369</t>
+          <t>169037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185657</t>
+          <t>185857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236303</t>
+          <t>237158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215425</t>
+          <t>216533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244428</t>
+          <t>244330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1079090</t>
+          <t>1076422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1121296</t>
+          <t>1118511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1305661</t>
+          <t>1304806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356307</t>
+          <t>1356107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>471991</t>
+          <t>471571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>560085</t>
+          <t>555106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>381206</t>
+          <t>383512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>458407</t>
+          <t>458242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>873602</t>
+          <t>881155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>987858</t>
+          <t>990373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2702426</t>
+          <t>2707405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2790520</t>
+          <t>2790940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2911519</t>
+          <t>2911684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2988720</t>
+          <t>2986414</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5644579</t>
+          <t>5642064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5758835</t>
+          <t>5751282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106900</t>
+          <t>108403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>54223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>111235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152541</t>
+          <t>152248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329300</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363268</t>
+          <t>363529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258299</t>
+          <t>258267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281758</t>
+          <t>281675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596149</t>
+          <t>596442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>638259</t>
+          <t>637455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44464</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74763</t>
+          <t>76867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72273</t>
+          <t>72816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96006</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137699</t>
+          <t>135893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336756</t>
+          <t>334652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367055</t>
+          <t>366977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262723</t>
+          <t>262180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293245</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608816</t>
+          <t>610622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650509</t>
+          <t>652142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79579</t>
+          <t>77709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117183</t>
+          <t>114174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45649</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109779</t>
+          <t>109676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152892</t>
+          <t>152444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511297</t>
+          <t>514306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>548901</t>
+          <t>550771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210178</t>
+          <t>209392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230721</t>
+          <t>230884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>731415</t>
+          <t>731863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>774528</t>
+          <t>774631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159075</t>
+          <t>159593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209965</t>
+          <t>211619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91717</t>
+          <t>92352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132920</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263135</t>
+          <t>263046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326634</t>
+          <t>326104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>936369</t>
+          <t>934715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>987259</t>
+          <t>986741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628435</t>
+          <t>628764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>669638</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1581055</t>
+          <t>1581585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1644554</t>
+          <t>1644643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66348</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>97682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95709</t>
+          <t>97973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140191</t>
+          <t>137628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188112</t>
+          <t>185372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408988</t>
+          <t>410084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>441418</t>
+          <t>441578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662506</t>
+          <t>660242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>696795</t>
+          <t>696663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1077868</t>
+          <t>1080608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1125789</t>
+          <t>1128352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101192</t>
+          <t>102074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>130273</t>
+          <t>130898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175523</t>
+          <t>175790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>211180</t>
+          <t>214642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>269028</t>
+          <t>269447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162687</t>
+          <t>161805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>190799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>916838</t>
+          <t>916571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>962088</t>
+          <t>961463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1087212</t>
+          <t>1086793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1145060</t>
+          <t>1141598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>554090</t>
+          <t>552603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>640850</t>
+          <t>643051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>432600</t>
+          <t>435502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>517127</t>
+          <t>514561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1012333</t>
+          <t>1010035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1132855</t>
+          <t>1132651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2753329</t>
+          <t>2751128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2840089</t>
+          <t>2841576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2998116</t>
+          <t>3000682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3082643</t>
+          <t>3079741</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5776567</t>
+          <t>5776771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5897089</t>
+          <t>5899387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55406</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>86599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53379</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82827</t>
+          <t>84097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117410</t>
+          <t>117541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158700</t>
+          <t>160921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>336996</t>
+          <t>338724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>369917</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258814</t>
+          <t>257544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288262</t>
+          <t>287999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608264</t>
+          <t>606043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>649554</t>
+          <t>649423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>46829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75841</t>
+          <t>75082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87905</t>
+          <t>86498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>126679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316073</t>
+          <t>313668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341808</t>
+          <t>340027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293084</t>
+          <t>293843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322190</t>
+          <t>322096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616664</t>
+          <t>616539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655313</t>
+          <t>656720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50378</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81034</t>
+          <t>81587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>67381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104885</t>
+          <t>103035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>435311</t>
+          <t>434758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465967</t>
+          <t>466717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137723</t>
+          <t>137556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154314</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577582</t>
+          <t>579432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614291</t>
+          <t>615086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120901</t>
+          <t>121950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166001</t>
+          <t>167051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94081</t>
+          <t>93058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133605</t>
+          <t>134124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226497</t>
+          <t>225557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284740</t>
+          <t>282699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>972373</t>
+          <t>971323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1017473</t>
+          <t>1016424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687524</t>
+          <t>687005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>727048</t>
+          <t>728071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1674764</t>
+          <t>1676805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1733007</t>
+          <t>1733947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76084</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56104</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86701</t>
+          <t>86301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107183</t>
+          <t>109806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152496</t>
+          <t>152266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543730</t>
+          <t>543235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>574999</t>
+          <t>574463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>646198</t>
+          <t>646598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676795</t>
+          <t>678974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200216</t>
+          <t>1200446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245529</t>
+          <t>1242906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80377</t>
+          <t>80822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>128876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173099</t>
+          <t>175089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189777</t>
+          <t>191337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243552</t>
+          <t>244278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202118</t>
+          <t>201673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230327</t>
+          <t>230601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>901447</t>
+          <t>899457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>947563</t>
+          <t>945670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1113489</t>
+          <t>1112763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1167264</t>
+          <t>1165704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>410988</t>
+          <t>411139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>488731</t>
+          <t>490971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>437204</t>
+          <t>437246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>516017</t>
+          <t>519968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>873389</t>
+          <t>868154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>987299</t>
+          <t>982395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2867913</t>
+          <t>2865673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2945656</t>
+          <t>2945505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2989245</t>
+          <t>2985294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3068058</t>
+          <t>3068016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5874607</t>
+          <t>5879511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5988517</t>
+          <t>5993752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75317</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93078</t>
+          <t>110554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>44342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64417</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>127557</t>
+          <t>144582</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108156</t>
+          <t>122676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149117</t>
+          <t>167448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>429895</t>
+          <t>462404</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412134</t>
+          <t>440064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446701</t>
+          <t>478299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>395227</t>
+          <t>432044</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383050</t>
+          <t>419054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>406868</t>
+          <t>444069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>825122</t>
+          <t>894447</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803562</t>
+          <t>871581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844523</t>
+          <t>916353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>78099</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>61810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92175</t>
+          <t>96364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57099</t>
+          <t>62477</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46763</t>
+          <t>51443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69489</t>
+          <t>75863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>130410</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108415</t>
+          <t>121121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152462</t>
+          <t>165447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>378902</t>
+          <t>405113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360038</t>
+          <t>386848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395491</t>
+          <t>421402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>325481</t>
+          <t>360666</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313091</t>
+          <t>347280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335817</t>
+          <t>371700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>704383</t>
+          <t>765779</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>682331</t>
+          <t>740908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726378</t>
+          <t>785234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>82962</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26145</t>
+          <t>67040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122444</t>
+          <t>101578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,17 +9354,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97673</t>
+          <t>110806</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36852</t>
+          <t>91929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146591</t>
+          <t>131794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>593972</t>
+          <t>387293</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544408</t>
+          <t>368677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640707</t>
+          <t>403215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,17 +9467,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141569</t>
+          <t>159016</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>149375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148527</t>
+          <t>166628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>735541</t>
+          <t>546310</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686623</t>
+          <t>525322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796362</t>
+          <t>565187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>148905</t>
+          <t>170472</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173361</t>
+          <t>199026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>103016</t>
+          <t>115449</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>97681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138882</t>
+          <t>135896</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>251921</t>
+          <t>285921</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173292</t>
+          <t>254905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296955</t>
+          <t>319564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>881503</t>
+          <t>956738</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>857047</t>
+          <t>928184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>905501</t>
+          <t>980992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>874388</t>
+          <t>745004</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>838522</t>
+          <t>724557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924255</t>
+          <t>762772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1755890</t>
+          <t>1701742</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1710856</t>
+          <t>1668099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1834519</t>
+          <t>1732758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>107993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73859</t>
+          <t>87979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113211</t>
+          <t>130933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>101234</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75964</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121508</t>
+          <t>129738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>194106</t>
+          <t>220319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156264</t>
+          <t>194410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223764</t>
+          <t>252325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>380709</t>
+          <t>458464</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360371</t>
+          <t>435524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399723</t>
+          <t>478478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>739441</t>
+          <t>717765</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719167</t>
+          <t>700352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>764711</t>
+          <t>733687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1120151</t>
+          <t>1176229</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1090493</t>
+          <t>1144223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1157993</t>
+          <t>1202138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79032</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>106245</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>87699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118671</t>
+          <t>126954</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>150518</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123575</t>
+          <t>130847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182911</t>
+          <t>190711</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>189490</t>
+          <t>184238</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161475</t>
+          <t>159445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207693</t>
+          <t>203574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>661276</t>
+          <t>737427</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>642107</t>
+          <t>716718</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>679597</t>
+          <t>755973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>850767</t>
+          <t>921665</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>818374</t>
+          <t>890189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>877710</t>
+          <t>950053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>514301</t>
+          <t>580732</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>414936</t>
+          <t>532252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>582146</t>
+          <t>631501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>437885</t>
+          <t>480708</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>439130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490315</t>
+          <t>521032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>952186</t>
+          <t>1061439</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>830190</t>
+          <t>996245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1041961</t>
+          <t>1124306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2854472</t>
+          <t>2854249</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2786627</t>
+          <t>2803480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2953837</t>
+          <t>2902729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3137380</t>
+          <t>3151921</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3084950</t>
+          <t>3111597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3226596</t>
+          <t>3193499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5991853</t>
+          <t>6006171</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5902078</t>
+          <t>5943304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6113849</t>
+          <t>6071365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
